--- a/artfynd/A 2274-2024 artfynd.xlsx
+++ b/artfynd/A 2274-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2274-2024 artfynd.xlsx
+++ b/artfynd/A 2274-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86442980</v>
+        <v>86442982</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>719493.1531570543</v>
+        <v>719435</v>
       </c>
       <c r="R2" t="n">
-        <v>7112599.924573416</v>
+        <v>7112461</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86442982</v>
+        <v>86442980</v>
       </c>
       <c r="B3" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>719434.842811477</v>
+        <v>719493</v>
       </c>
       <c r="R3" t="n">
-        <v>7112460.998324964</v>
+        <v>7112600</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-06-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86442981</v>
+        <v>86442979</v>
       </c>
       <c r="B4" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>719429.0720406031</v>
+        <v>719461</v>
       </c>
       <c r="R4" t="n">
-        <v>7112474.201659415</v>
+        <v>7112598</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-06-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86442977</v>
+        <v>86442981</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>719485.203351425</v>
+        <v>719429</v>
       </c>
       <c r="R5" t="n">
-        <v>7112712.201454742</v>
+        <v>7112474</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-06-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-06-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86442979</v>
+        <v>86442977</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719461.1886680415</v>
+        <v>719485</v>
       </c>
       <c r="R6" t="n">
-        <v>7112598.100564218</v>
+        <v>7112712</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2020-06-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-06-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,6 +1173,107 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>86442978</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Länningsberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>719407</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7112631</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-06-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-06-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>

--- a/artfynd/A 2274-2024 artfynd.xlsx
+++ b/artfynd/A 2274-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86442982</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86442980</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86442979</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86442981</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86442977</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86442978</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>